--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFC3456-2781-4840-9BBA-1F53B1514E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0729D6DE-2382-44ED-AFAE-8CA037DDE780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_summon_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,6 +168,22 @@
   </si>
   <si>
     <t>守卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时存在数量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_number</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,28 +520,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -545,14 +562,14 @@
         <v>12</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" s="2" t="s">
         <v>12</v>
       </c>
@@ -571,8 +588,14 @@
       <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -586,40 +609,46 @@
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -633,40 +662,46 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -677,28 +712,28 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
         <v>800001041</v>
       </c>
-      <c r="F5" s="2">
+      <c r="H5" s="2">
         <v>201004011</v>
       </c>
-      <c r="G5" s="2">
+      <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
+        <v>-10000</v>
+      </c>
+      <c r="K5" s="2">
         <v>15000</v>
       </c>
-      <c r="J5" s="2">
+      <c r="L5" s="2">
         <v>10000</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
@@ -707,6 +742,12 @@
         <v>0</v>
       </c>
       <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0729D6DE-2382-44ED-AFAE-8CA037DDE780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BFD670-99B9-483A-9DB2-4D108F3ABA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_summon_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,33 +157,38 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>召唤物描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时存在数量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>STRING</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>召唤物描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>守卫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时存在数量上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -547,10 +552,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -603,16 +608,16 @@
         <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>6</v>
@@ -656,16 +661,16 @@
         <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>7</v>
@@ -706,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BFD670-99B9-483A-9DB2-4D108F3ABA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FAE83-7D98-4CE4-91CF-F5D2330C161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,10 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>守卫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持续时间（毫秒）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,6 +185,10 @@
   </si>
   <si>
     <t>STRING_C_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火龙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -552,10 +552,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -614,10 +614,10 @@
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>6</v>
@@ -667,10 +667,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>7</v>
@@ -711,19 +711,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" s="2">
-        <v>800001041</v>
+        <v>900000001</v>
       </c>
       <c r="H5" s="2">
         <v>201004011</v>
@@ -735,7 +735,7 @@
         <v>-10000</v>
       </c>
       <c r="K5" s="2">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="L5" s="2">
         <v>10000</v>

--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FAE83-7D98-4CE4-91CF-F5D2330C161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4417443C-938D-4B51-B4A9-3B3F94637350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,7 +726,7 @@
         <v>900000001</v>
       </c>
       <c r="H5" s="2">
-        <v>201004011</v>
+        <v>200801001</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12225"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_summon_v8" sheetId="1" r:id="rId1"/>
@@ -165,7 +165,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,13 +178,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -634,148 +627,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1296,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="F5" s="1">
         <v>6</v>

--- a/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_summon_v8【迷宫-召唤物】.xlsx
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="1">
         <v>6</v>
